--- a/IT002-OOP/Điểm thực hành/it002q216/IT002.Q216.1.xlsx
+++ b/IT002-OOP/Điểm thực hành/it002q216/IT002.Q216.1.xlsx
@@ -1,21 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11214"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vutuanhai/Desktop/Important/CourseMaterials/IT002-OOP/Điểm thực hành/it002q216/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CB58626-BDDD-C04E-87B6-49E37041C9D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="16720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="IT002.Q216.1" sheetId="1" r:id="rId4"/>
+    <sheet name="IT002.Q216.1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="110">
   <si>
     <t>TRƯỜNG ĐH CÔNG NGHỆ THÔNG TIN</t>
   </si>
@@ -352,118 +357,89 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0#######"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="1"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <i/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="1"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <i/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -551,123 +527,130 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="7" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="8" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="164" fillId="0" borderId="4" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="7" numFmtId="0" fillId="0" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="9" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="10" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="10" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="10" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="7" numFmtId="0" fillId="0" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="9" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="7" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="11" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+  <cellXfs count="43">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -957,30 +940,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I55"/>
-  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="8.83203125" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="true" style="0"/>
-    <col min="2" max="2" width="10.1640625" customWidth="true" style="0"/>
-    <col min="3" max="3" width="23" customWidth="true" style="0"/>
-    <col min="4" max="4" width="9.5" customWidth="true" style="0"/>
-    <col min="5" max="5" width="12.6640625" customWidth="true" style="0"/>
-    <col min="6" max="6" width="9" customWidth="true" style="0"/>
-    <col min="7" max="7" width="12.83203125" customWidth="true" style="0"/>
-    <col min="8" max="8" width="13.33203125" customWidth="true" style="0"/>
-    <col min="9" max="9" width="25.5" customWidth="true" style="0"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="2" max="2" width="10.1640625" customWidth="1"/>
+    <col min="3" max="3" width="23" customWidth="1"/>
+    <col min="4" max="4" width="9.5" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" customWidth="1"/>
+    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="13.33203125" customWidth="1"/>
+    <col min="9" max="9" width="25.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" customHeight="1" ht="16">
-      <c r="A1" s="40" t="s">
+    <row r="1" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
       <c r="D1" s="9"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -988,23 +968,21 @@
       <c r="H1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="I1"/>
-    </row>
-    <row r="2" spans="1:9" customHeight="1" ht="15">
-      <c r="A2" s="41" t="s">
+    </row>
+    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-      <c r="I2"/>
-    </row>
-    <row r="3" spans="1:9" customHeight="1" ht="15">
-      <c r="A3" s="16"/>
+    </row>
+    <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="15"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -1012,102 +990,96 @@
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
-      <c r="I3"/>
-    </row>
-    <row r="4" spans="1:9" customHeight="1" ht="20">
-      <c r="A4" s="42" t="s">
+    </row>
+    <row r="4" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="42"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4"/>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="43" t="s">
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A5" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="15">
+      <c r="B5" s="35"/>
+      <c r="C5" s="14">
         <v>2</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="14">
         <v>2025</v>
       </c>
       <c r="F5" s="10"/>
       <c r="G5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="H5" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I5"/>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="33" t="s">
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A6" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="33"/>
+      <c r="B6" s="34"/>
       <c r="C6" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="16" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="17"/>
-      <c r="I6"/>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="33" t="s">
+      <c r="H6" s="16"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A7" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="33"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="16" t="s">
         <v>16</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="17"/>
-      <c r="I7"/>
-    </row>
-    <row r="8" spans="1:9" customHeight="1" ht="15">
-      <c r="A8" s="33" t="s">
+      <c r="H7" s="16"/>
+    </row>
+    <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="33"/>
+      <c r="B8" s="34"/>
       <c r="C8" s="4">
         <v>80503</v>
       </c>
-      <c r="D8" s="18"/>
+      <c r="D8" s="17"/>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
-      <c r="I8"/>
-    </row>
-    <row r="9" spans="1:9" customHeight="1" ht="15">
+    </row>
+    <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
@@ -1116,765 +1088,831 @@
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
-      <c r="I9"/>
-    </row>
-    <row r="10" spans="1:9" customHeight="1" ht="30">
+    </row>
+    <row r="10" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G10" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="H10" s="19" t="s">
+      <c r="H10" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="I10" s="19" t="s">
+      <c r="I10" s="18" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:9" customHeight="1" ht="14">
-      <c r="A11" s="20">
+    <row r="11" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="19">
         <v>1</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="23"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" customHeight="1" ht="14">
-      <c r="A12" s="20">
+      <c r="D11" s="22"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="1">
+        <v>6.6</v>
+      </c>
+      <c r="G11" s="22"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="19">
         <v>2</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="D12" s="23"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="25"/>
-      <c r="I12" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" customHeight="1" ht="14">
-      <c r="A13" s="20">
+      <c r="D12" s="22"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="G12" s="22"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="19">
         <v>3</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="D13" s="23"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="25"/>
-      <c r="I13" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" customHeight="1" ht="14">
-      <c r="A14" s="20">
+      <c r="D13" s="22"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="G13" s="22"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="19">
         <v>4</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="D14" s="23"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="25"/>
-      <c r="I14" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" customHeight="1" ht="14">
-      <c r="A15" s="20">
+      <c r="D14" s="22"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="1">
+        <v>6.7</v>
+      </c>
+      <c r="G14" s="22"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="19">
         <v>5</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="D15" s="23"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" customHeight="1" ht="14">
-      <c r="A16" s="20">
+      <c r="D15" s="22"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="G15" s="22"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="19">
         <v>6</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="D16" s="23"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" customHeight="1" ht="14">
-      <c r="A17" s="20">
+      <c r="D16" s="22"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="1">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="G16" s="22"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="19">
         <v>7</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C17" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="D17" s="23"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" customHeight="1" ht="14">
-      <c r="A18" s="20">
+      <c r="D17" s="22"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="1">
+        <v>7.7</v>
+      </c>
+      <c r="G17" s="22"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="19">
         <v>8</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="D18" s="23"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="25"/>
-      <c r="I18" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" customHeight="1" ht="14">
-      <c r="A19" s="20">
+      <c r="D18" s="22"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="1">
+        <v>6.4</v>
+      </c>
+      <c r="G18" s="22"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="19">
         <v>9</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="22" t="s">
+      <c r="C19" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="D19" s="23"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" customHeight="1" ht="14">
-      <c r="A20" s="20">
+      <c r="D19" s="22"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="G19" s="22"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="19">
         <v>10</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="C20" s="22" t="s">
+      <c r="C20" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="D20" s="23"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="23"/>
-      <c r="H20" s="25"/>
-      <c r="I20" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" customHeight="1" ht="14">
-      <c r="A21" s="20">
+      <c r="D20" s="22"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="1">
+        <v>7.3</v>
+      </c>
+      <c r="G20" s="22"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="19">
         <v>11</v>
       </c>
-      <c r="B21" s="21" t="s">
+      <c r="B21" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="22" t="s">
+      <c r="C21" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="D21" s="23"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="25"/>
-      <c r="I21" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" customHeight="1" ht="14">
-      <c r="A22" s="20">
+      <c r="D21" s="22"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="G21" s="22"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="19">
         <v>12</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="C22" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="23"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" customHeight="1" ht="14">
-      <c r="A23" s="20">
+      <c r="D22" s="22"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="1">
+        <v>9</v>
+      </c>
+      <c r="G22" s="22"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="19">
         <v>13</v>
       </c>
-      <c r="B23" s="21" t="s">
+      <c r="B23" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="22" t="s">
+      <c r="C23" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D23" s="23"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="25"/>
-      <c r="I23" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" customHeight="1" ht="14">
-      <c r="A24" s="20">
+      <c r="D23" s="22"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="1">
+        <v>7.4</v>
+      </c>
+      <c r="G23" s="22"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="19">
         <v>14</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="22" t="s">
+      <c r="C24" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="D24" s="23"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="25"/>
-      <c r="I24" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" customHeight="1" ht="14">
-      <c r="A25" s="20">
+      <c r="D24" s="22"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="1">
+        <v>7.4</v>
+      </c>
+      <c r="G24" s="22"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="19">
         <v>15</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="C25" s="22" t="s">
+      <c r="C25" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="D25" s="23"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="25"/>
-      <c r="I25" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" customHeight="1" ht="14">
-      <c r="A26" s="20">
+      <c r="D25" s="22"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="1">
+        <v>5.3</v>
+      </c>
+      <c r="G25" s="22"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="19">
         <v>16</v>
       </c>
-      <c r="B26" s="21" t="s">
+      <c r="B26" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C26" s="22" t="s">
+      <c r="C26" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="23"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="25"/>
-      <c r="I26" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" customHeight="1" ht="14">
-      <c r="A27" s="20">
+      <c r="D26" s="22"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="1">
+        <v>9</v>
+      </c>
+      <c r="G26" s="22"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="19">
         <v>17</v>
       </c>
-      <c r="B27" s="21" t="s">
+      <c r="B27" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="22" t="s">
+      <c r="C27" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="D27" s="23"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="25"/>
-      <c r="I27" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" customHeight="1" ht="14">
-      <c r="A28" s="20">
+      <c r="D27" s="22"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="1">
+        <v>8.4</v>
+      </c>
+      <c r="G27" s="22"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="19">
         <v>18</v>
       </c>
-      <c r="B28" s="21" t="s">
+      <c r="B28" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="C28" s="22" t="s">
+      <c r="C28" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="D28" s="23"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="25"/>
-      <c r="I28" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" customHeight="1" ht="14">
-      <c r="A29" s="20">
+      <c r="D28" s="22"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="1">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="G28" s="22"/>
+      <c r="H28" s="24"/>
+      <c r="I28" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="19">
         <v>19</v>
       </c>
-      <c r="B29" s="21" t="s">
+      <c r="B29" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="C29" s="22" t="s">
+      <c r="C29" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="D29" s="23"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="25"/>
-      <c r="I29" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" customHeight="1" ht="14">
-      <c r="A30" s="20">
+      <c r="D29" s="22"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="G29" s="22"/>
+      <c r="H29" s="24"/>
+      <c r="I29" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="19">
         <v>20</v>
       </c>
-      <c r="B30" s="21" t="s">
+      <c r="B30" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="C30" s="22" t="s">
+      <c r="C30" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="D30" s="23"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="23"/>
-      <c r="H30" s="25"/>
-      <c r="I30" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" customHeight="1" ht="14">
-      <c r="A31" s="20">
+      <c r="D30" s="22"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="1">
+        <v>7.9</v>
+      </c>
+      <c r="G30" s="22"/>
+      <c r="H30" s="24"/>
+      <c r="I30" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="19">
         <v>21</v>
       </c>
-      <c r="B31" s="21" t="s">
+      <c r="B31" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="22" t="s">
+      <c r="C31" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="D31" s="23"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="23"/>
-      <c r="H31" s="25"/>
-      <c r="I31" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" customHeight="1" ht="14">
-      <c r="A32" s="20">
+      <c r="D31" s="22"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="G31" s="22"/>
+      <c r="H31" s="24"/>
+      <c r="I31" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="19">
         <v>22</v>
       </c>
-      <c r="B32" s="21" t="s">
+      <c r="B32" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="22" t="s">
+      <c r="C32" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="D32" s="23"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="23"/>
-      <c r="H32" s="25"/>
-      <c r="I32" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" customHeight="1" ht="14">
-      <c r="A33" s="20">
+      <c r="D32" s="22"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="1">
+        <v>8.4</v>
+      </c>
+      <c r="G32" s="22"/>
+      <c r="H32" s="24"/>
+      <c r="I32" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="19">
         <v>23</v>
       </c>
-      <c r="B33" s="21" t="s">
+      <c r="B33" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="C33" s="22" t="s">
+      <c r="C33" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="D33" s="23"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="23"/>
-      <c r="H33" s="25"/>
-      <c r="I33" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" customHeight="1" ht="14">
-      <c r="A34" s="20">
+      <c r="D33" s="22"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="1">
+        <v>7.6</v>
+      </c>
+      <c r="G33" s="22"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="19">
         <v>24</v>
       </c>
-      <c r="B34" s="21" t="s">
+      <c r="B34" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="C34" s="22" t="s">
+      <c r="C34" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="D34" s="23"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="23"/>
-      <c r="G34" s="23"/>
-      <c r="H34" s="25"/>
-      <c r="I34" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" customHeight="1" ht="14">
-      <c r="A35" s="20">
+      <c r="D34" s="22"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="1">
+        <v>2</v>
+      </c>
+      <c r="G34" s="22"/>
+      <c r="H34" s="24"/>
+      <c r="I34" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="19">
         <v>25</v>
       </c>
-      <c r="B35" s="21" t="s">
+      <c r="B35" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="C35" s="22" t="s">
+      <c r="C35" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="D35" s="23"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="23"/>
-      <c r="G35" s="23"/>
-      <c r="H35" s="25"/>
-      <c r="I35" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" customHeight="1" ht="14">
-      <c r="A36" s="20">
+      <c r="D35" s="22"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="G35" s="22"/>
+      <c r="H35" s="24"/>
+      <c r="I35" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="19">
         <v>26</v>
       </c>
-      <c r="B36" s="21" t="s">
+      <c r="B36" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="C36" s="22" t="s">
+      <c r="C36" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="D36" s="23"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="23"/>
-      <c r="G36" s="23"/>
-      <c r="H36" s="25"/>
-      <c r="I36" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" customHeight="1" ht="14">
-      <c r="A37" s="20">
+      <c r="D36" s="22"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="1">
+        <v>7.2</v>
+      </c>
+      <c r="G36" s="22"/>
+      <c r="H36" s="24"/>
+      <c r="I36" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="19">
         <v>27</v>
       </c>
-      <c r="B37" s="21" t="s">
+      <c r="B37" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="C37" s="22" t="s">
+      <c r="C37" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="D37" s="23"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="23"/>
-      <c r="H37" s="25"/>
-      <c r="I37" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" customHeight="1" ht="14">
-      <c r="A38" s="20">
+      <c r="D37" s="22"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="1">
+        <v>9.1</v>
+      </c>
+      <c r="G37" s="22"/>
+      <c r="H37" s="24"/>
+      <c r="I37" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="19">
         <v>28</v>
       </c>
-      <c r="B38" s="21" t="s">
+      <c r="B38" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C38" s="22" t="s">
+      <c r="C38" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D38" s="23"/>
-      <c r="E38" s="24"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="23"/>
-      <c r="H38" s="25"/>
-      <c r="I38" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" customHeight="1" ht="14">
-      <c r="A39" s="20">
+      <c r="D38" s="22"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="G38" s="22"/>
+      <c r="H38" s="24"/>
+      <c r="I38" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="19">
         <v>29</v>
       </c>
-      <c r="B39" s="21" t="s">
+      <c r="B39" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="C39" s="22" t="s">
+      <c r="C39" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="D39" s="23"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="23"/>
-      <c r="G39" s="23"/>
-      <c r="H39" s="25"/>
-      <c r="I39" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" customHeight="1" ht="14">
-      <c r="A40" s="20">
-        <v>30</v>
-      </c>
-      <c r="B40" s="21" t="s">
+      <c r="D39" s="22"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="1">
+        <v>8.9</v>
+      </c>
+      <c r="G39" s="22"/>
+      <c r="H39" s="24"/>
+      <c r="I39" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="19">
+        <v>30</v>
+      </c>
+      <c r="B40" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="C40" s="22" t="s">
+      <c r="C40" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="D40" s="23"/>
-      <c r="E40" s="24"/>
-      <c r="F40" s="23"/>
-      <c r="G40" s="23"/>
-      <c r="H40" s="25"/>
-      <c r="I40" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" customHeight="1" ht="14">
-      <c r="A41" s="20">
+      <c r="D40" s="22"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="1">
+        <v>9</v>
+      </c>
+      <c r="G40" s="22"/>
+      <c r="H40" s="24"/>
+      <c r="I40" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="19">
         <v>31</v>
       </c>
-      <c r="B41" s="21" t="s">
+      <c r="B41" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="C41" s="22" t="s">
+      <c r="C41" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="D41" s="23"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="23"/>
-      <c r="G41" s="23"/>
-      <c r="H41" s="25"/>
-      <c r="I41" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" customHeight="1" ht="14">
-      <c r="A42" s="20">
+      <c r="D41" s="22"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="G41" s="22"/>
+      <c r="H41" s="24"/>
+      <c r="I41" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="19">
         <v>32</v>
       </c>
-      <c r="B42" s="21" t="s">
+      <c r="B42" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="C42" s="22" t="s">
+      <c r="C42" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="D42" s="23"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="23"/>
-      <c r="G42" s="23"/>
-      <c r="H42" s="25"/>
-      <c r="I42" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" customHeight="1" ht="14">
-      <c r="A43" s="20">
+      <c r="D42" s="22"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="G42" s="22"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="19">
         <v>33</v>
       </c>
-      <c r="B43" s="21" t="s">
+      <c r="B43" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="C43" s="22" t="s">
+      <c r="C43" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="D43" s="23"/>
-      <c r="E43" s="24"/>
-      <c r="F43" s="23"/>
-      <c r="G43" s="23"/>
-      <c r="H43" s="25"/>
-      <c r="I43" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" customHeight="1" ht="14">
-      <c r="A44" s="20">
+      <c r="D43" s="22"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="1">
+        <v>7.1</v>
+      </c>
+      <c r="G43" s="22"/>
+      <c r="H43" s="24"/>
+      <c r="I43" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="19">
         <v>34</v>
       </c>
-      <c r="B44" s="21" t="s">
+      <c r="B44" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="C44" s="22" t="s">
+      <c r="C44" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="D44" s="23"/>
-      <c r="E44" s="24"/>
-      <c r="F44" s="23"/>
-      <c r="G44" s="23"/>
-      <c r="H44" s="25"/>
-      <c r="I44" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" customHeight="1" ht="14">
-      <c r="A45" s="20">
+      <c r="D44" s="22"/>
+      <c r="E44" s="23"/>
+      <c r="F44" s="1">
+        <v>7.4</v>
+      </c>
+      <c r="G44" s="22"/>
+      <c r="H44" s="24"/>
+      <c r="I44" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="19">
         <v>35</v>
       </c>
-      <c r="B45" s="21" t="s">
+      <c r="B45" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="C45" s="22" t="s">
+      <c r="C45" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="D45" s="23"/>
-      <c r="E45" s="24"/>
-      <c r="F45" s="23"/>
-      <c r="G45" s="23"/>
-      <c r="H45" s="25"/>
-      <c r="I45" s="25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" customHeight="1" ht="14">
-      <c r="A46" s="20"/>
-      <c r="B46" s="21"/>
-      <c r="C46" s="22"/>
-      <c r="D46" s="23"/>
-      <c r="E46" s="24"/>
-      <c r="F46" s="23"/>
-      <c r="G46" s="23"/>
-      <c r="H46" s="25"/>
-      <c r="I46" s="25"/>
-    </row>
-    <row r="47" spans="1:9" customHeight="1" ht="15">
+      <c r="D45" s="22"/>
+      <c r="E45" s="23"/>
+      <c r="F45" s="1">
+        <v>7.7</v>
+      </c>
+      <c r="G45" s="22"/>
+      <c r="H45" s="24"/>
+      <c r="I45" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="19"/>
+      <c r="B46" s="20"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="22"/>
+      <c r="E46" s="23"/>
+      <c r="F46" s="22"/>
+      <c r="G46" s="22"/>
+      <c r="H46" s="24"/>
+      <c r="I46" s="24"/>
+    </row>
+    <row r="47" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12"/>
-      <c r="B47" s="26"/>
-      <c r="C47" s="27"/>
-      <c r="D47" s="34" t="s">
+      <c r="B47" s="25"/>
+      <c r="C47" s="26"/>
+      <c r="D47" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="E47" s="34"/>
-      <c r="F47" s="34"/>
-      <c r="G47" s="34"/>
-      <c r="H47" s="34"/>
-      <c r="I47"/>
-    </row>
-    <row r="48" spans="1:9">
-      <c r="A48" s="35" t="s">
+      <c r="E47" s="37"/>
+      <c r="F47" s="37"/>
+      <c r="G47" s="37"/>
+      <c r="H47" s="37"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A48" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="B48" s="35"/>
-      <c r="C48" s="28" t="s">
+      <c r="B48" s="38"/>
+      <c r="C48" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="D48" s="36" t="s">
+      <c r="D48" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="E48" s="37"/>
-      <c r="F48" s="38" t="s">
+      <c r="E48" s="40"/>
+      <c r="F48" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="G48" s="37"/>
-      <c r="H48" s="37"/>
-      <c r="I48"/>
-    </row>
-    <row r="49" spans="1:9">
-      <c r="A49" s="39" t="s">
+      <c r="G48" s="40"/>
+      <c r="H48" s="40"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A49" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="B49" s="39"/>
-      <c r="C49" s="29" t="s">
+      <c r="B49" s="42"/>
+      <c r="C49" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="D49" s="39" t="s">
+      <c r="D49" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="E49" s="39"/>
-      <c r="F49" s="39" t="s">
+      <c r="E49" s="42"/>
+      <c r="F49" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="G49" s="39"/>
-      <c r="H49" s="39"/>
-      <c r="I49"/>
-    </row>
-    <row r="50" spans="1:9" customHeight="1" ht="15">
+      <c r="G49" s="42"/>
+      <c r="H49" s="42"/>
+    </row>
+    <row r="50" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="12"/>
       <c r="B50" s="8"/>
       <c r="C50" s="1"/>
@@ -1883,84 +1921,63 @@
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
-      <c r="I50"/>
-    </row>
-    <row r="51" spans="1:9">
-      <c r="A51" s="14"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51"/>
-    </row>
-    <row r="52" spans="1:9">
-      <c r="A52" s="30" t="s">
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A52" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="B52" s="30"/>
-      <c r="C52" s="30"/>
-      <c r="D52" s="30"/>
-      <c r="E52" s="30"/>
-      <c r="F52" s="30"/>
-      <c r="G52" s="30"/>
-      <c r="H52" s="30"/>
-      <c r="I52"/>
-    </row>
-    <row r="53" spans="1:9">
-      <c r="A53" s="31" t="s">
+      <c r="B52" s="29"/>
+      <c r="C52" s="29"/>
+      <c r="D52" s="29"/>
+      <c r="E52" s="29"/>
+      <c r="F52" s="29"/>
+      <c r="G52" s="29"/>
+      <c r="H52" s="29"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A53" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="B53" s="32" t="s">
+      <c r="B53" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="C53" s="32"/>
-      <c r="D53" s="32"/>
-      <c r="E53" s="32"/>
-      <c r="F53" s="32"/>
-      <c r="G53" s="32"/>
-      <c r="H53" s="32"/>
-      <c r="I53"/>
-    </row>
-    <row r="54" spans="1:9">
-      <c r="A54" s="31" t="s">
+      <c r="C53" s="36"/>
+      <c r="D53" s="36"/>
+      <c r="E53" s="36"/>
+      <c r="F53" s="36"/>
+      <c r="G53" s="36"/>
+      <c r="H53" s="36"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A54" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="B54" s="32" t="s">
+      <c r="B54" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="C54" s="32"/>
-      <c r="D54" s="32"/>
-      <c r="E54" s="32"/>
-      <c r="F54" s="32"/>
-      <c r="G54" s="32"/>
-      <c r="H54" s="32"/>
-      <c r="I54"/>
-    </row>
-    <row r="55" spans="1:9">
-      <c r="A55" s="31" t="s">
+      <c r="C54" s="36"/>
+      <c r="D54" s="36"/>
+      <c r="E54" s="36"/>
+      <c r="F54" s="36"/>
+      <c r="G54" s="36"/>
+      <c r="H54" s="36"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A55" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="B55" s="32" t="s">
+      <c r="B55" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="C55" s="32"/>
-      <c r="D55" s="32"/>
-      <c r="E55" s="32"/>
-      <c r="F55" s="32"/>
-      <c r="G55" s="32"/>
-      <c r="H55" s="32"/>
-      <c r="I55"/>
+      <c r="C55" s="36"/>
+      <c r="D55" s="36"/>
+      <c r="E55" s="36"/>
+      <c r="F55" s="36"/>
+      <c r="G55" s="36"/>
+      <c r="H55" s="36"/>
     </row>
   </sheetData>
-  <mergeCells>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A5:B5"/>
+  <mergeCells count="17">
     <mergeCell ref="B53:H53"/>
     <mergeCell ref="B54:H54"/>
     <mergeCell ref="A7:B7"/>
@@ -1973,18 +1990,13 @@
     <mergeCell ref="A49:B49"/>
     <mergeCell ref="D49:E49"/>
     <mergeCell ref="F49:H49"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A5:B5"/>
   </mergeCells>
-  <printOptions gridLines="false" gridLinesSet="true"/>
-  <pageMargins left="0.26" right="0.17" top="0.32" bottom="0.29" header="0.25" footer="0.19"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
+  <pageMargins left="0.26" right="0.17" top="0.32" bottom="0.28999999999999998" header="0.25" footer="0.19"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
--- a/IT002-OOP/Điểm thực hành/it002q216/IT002.Q216.1.xlsx
+++ b/IT002-OOP/Điểm thực hành/it002q216/IT002.Q216.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vutuanhai/Desktop/Important/CourseMaterials/IT002-OOP/Điểm thực hành/it002q216/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CB58626-BDDD-C04E-87B6-49E37041C9D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04DC4F39-32AD-D847-B772-0463B94B67E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="16720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -603,22 +603,10 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -636,6 +624,18 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -956,11 +956,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
       <c r="D1" s="9"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -970,11 +970,11 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="1"/>
@@ -992,22 +992,22 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="35"/>
+      <c r="B5" s="42"/>
       <c r="C5" s="14">
         <v>2</v>
       </c>
@@ -1026,10 +1026,10 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="34"/>
+      <c r="B6" s="32"/>
       <c r="C6" s="4" t="s">
         <v>9</v>
       </c>
@@ -1046,10 +1046,10 @@
       <c r="H6" s="16"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="34"/>
+      <c r="B7" s="32"/>
       <c r="C7" s="4" t="s">
         <v>14</v>
       </c>
@@ -1066,10 +1066,10 @@
       <c r="H7" s="16"/>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="34"/>
+      <c r="B8" s="32"/>
       <c r="C8" s="4">
         <v>80503</v>
       </c>
@@ -1761,7 +1761,7 @@
       <c r="D41" s="22"/>
       <c r="E41" s="23"/>
       <c r="F41" s="1">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="G41" s="22"/>
       <c r="H41" s="24"/>
@@ -1782,7 +1782,7 @@
       <c r="D42" s="22"/>
       <c r="E42" s="23"/>
       <c r="F42" s="1">
-        <v>8.5</v>
+        <v>4.5</v>
       </c>
       <c r="G42" s="22"/>
       <c r="H42" s="24"/>
@@ -1868,49 +1868,49 @@
       <c r="A47" s="12"/>
       <c r="B47" s="25"/>
       <c r="C47" s="26"/>
-      <c r="D47" s="37" t="s">
+      <c r="D47" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="E47" s="37"/>
-      <c r="F47" s="37"/>
-      <c r="G47" s="37"/>
-      <c r="H47" s="37"/>
+      <c r="E47" s="33"/>
+      <c r="F47" s="33"/>
+      <c r="G47" s="33"/>
+      <c r="H47" s="33"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A48" s="38" t="s">
+      <c r="A48" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="B48" s="38"/>
+      <c r="B48" s="34"/>
       <c r="C48" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="D48" s="39" t="s">
+      <c r="D48" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="E48" s="40"/>
-      <c r="F48" s="41" t="s">
+      <c r="E48" s="36"/>
+      <c r="F48" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="G48" s="40"/>
-      <c r="H48" s="40"/>
+      <c r="G48" s="36"/>
+      <c r="H48" s="36"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A49" s="42" t="s">
+      <c r="A49" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="B49" s="42"/>
+      <c r="B49" s="38"/>
       <c r="C49" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="D49" s="42" t="s">
+      <c r="D49" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="E49" s="42"/>
-      <c r="F49" s="42" t="s">
+      <c r="E49" s="38"/>
+      <c r="F49" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="G49" s="42"/>
-      <c r="H49" s="42"/>
+      <c r="G49" s="38"/>
+      <c r="H49" s="38"/>
     </row>
     <row r="50" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="12"/>
@@ -1938,46 +1938,51 @@
       <c r="A53" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="B53" s="36" t="s">
+      <c r="B53" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="C53" s="36"/>
-      <c r="D53" s="36"/>
-      <c r="E53" s="36"/>
-      <c r="F53" s="36"/>
-      <c r="G53" s="36"/>
-      <c r="H53" s="36"/>
+      <c r="C53" s="31"/>
+      <c r="D53" s="31"/>
+      <c r="E53" s="31"/>
+      <c r="F53" s="31"/>
+      <c r="G53" s="31"/>
+      <c r="H53" s="31"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A54" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="B54" s="36" t="s">
+      <c r="B54" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="C54" s="36"/>
-      <c r="D54" s="36"/>
-      <c r="E54" s="36"/>
-      <c r="F54" s="36"/>
-      <c r="G54" s="36"/>
-      <c r="H54" s="36"/>
+      <c r="C54" s="31"/>
+      <c r="D54" s="31"/>
+      <c r="E54" s="31"/>
+      <c r="F54" s="31"/>
+      <c r="G54" s="31"/>
+      <c r="H54" s="31"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A55" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="B55" s="36" t="s">
+      <c r="B55" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="C55" s="36"/>
-      <c r="D55" s="36"/>
-      <c r="E55" s="36"/>
-      <c r="F55" s="36"/>
-      <c r="G55" s="36"/>
-      <c r="H55" s="36"/>
+      <c r="C55" s="31"/>
+      <c r="D55" s="31"/>
+      <c r="E55" s="31"/>
+      <c r="F55" s="31"/>
+      <c r="G55" s="31"/>
+      <c r="H55" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A5:B5"/>
     <mergeCell ref="B53:H53"/>
     <mergeCell ref="B54:H54"/>
     <mergeCell ref="A7:B7"/>
@@ -1990,11 +1995,6 @@
     <mergeCell ref="A49:B49"/>
     <mergeCell ref="D49:E49"/>
     <mergeCell ref="F49:H49"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A5:B5"/>
   </mergeCells>
   <pageMargins left="0.26" right="0.17" top="0.32" bottom="0.28999999999999998" header="0.25" footer="0.19"/>
   <pageSetup orientation="portrait"/>
